--- a/quote_automation/assets/steel_material_quote_template.xlsx
+++ b/quote_automation/assets/steel_material_quote_template.xlsx
@@ -368,7 +368,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -607,6 +607,9 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1020,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.08984375" customWidth="1" style="37" min="1" max="1"/>
@@ -1939,13 +1942,14 @@
           <t>原価</t>
         </is>
       </c>
-      <c r="O16" s="74" t="inlineStr">
-        <is>
-          <t>円/kg乗せ←入力</t>
-        </is>
-      </c>
+      <c r="O16" s="74" t="n"/>
       <c r="P16" s="75" t="n">
         <v>0</v>
+      </c>
+      <c r="Q16" s="88" t="inlineStr">
+        <is>
+          <t>円/kg乗せ</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -2319,7 +2323,10 @@
       <c r="G26" s="83" t="n"/>
       <c r="H26" s="27" t="n"/>
       <c r="I26" s="29" t="n"/>
-      <c r="J26" s="59" t="n"/>
+      <c r="J26" s="59">
+        <f>ROUND(P26*Q26,-3)</f>
+        <v/>
+      </c>
       <c r="K26" s="9" t="n"/>
       <c r="M26" s="58" t="inlineStr">
         <is>
@@ -2329,6 +2336,9 @@
       <c r="N26" s="27" t="n"/>
       <c r="O26" s="29" t="n"/>
       <c r="P26" s="80" t="n"/>
+      <c r="Q26" s="89" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1" thickBot="1">
       <c r="B27" s="60" t="inlineStr">
@@ -2363,6 +2373,15 @@
     <row r="28" ht="16" customHeight="1">
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="9" t="n"/>
+      <c r="M28" s="88" t="inlineStr">
+        <is>
+          <t>利益</t>
+        </is>
+      </c>
+      <c r="P28" s="90">
+        <f>J27-P27</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="16" customFormat="1" customHeight="1" s="11">
       <c r="B29" s="44" t="n"/>

--- a/quote_automation/assets/steel_material_quote_template.xlsx
+++ b/quote_automation/assets/steel_material_quote_template.xlsx
@@ -1037,11 +1037,11 @@
     <col width="10.36328125" customWidth="1" style="37" min="9" max="9"/>
     <col width="15" customWidth="1" style="37" min="10" max="10"/>
     <col width="8.90625" customWidth="1" style="37" min="11" max="12"/>
-    <col width="7.7265625" customWidth="1" style="37" min="13" max="13"/>
-    <col width="13.36328125" bestFit="1" customWidth="1" style="37" min="14" max="14"/>
-    <col width="11.26953125" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
-    <col width="13.6328125" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
-    <col width="8.90625" customWidth="1" style="37" min="17" max="242"/>
+    <col hidden="1" width="7.7265625" customWidth="1" style="37" min="13" max="13"/>
+    <col hidden="1" width="13.36328125" bestFit="1" customWidth="1" style="37" min="14" max="14"/>
+    <col hidden="1" width="11.26953125" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
+    <col hidden="1" width="13.6328125" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
+    <col hidden="1" width="8.90625" customWidth="1" style="37" min="17" max="242"/>
     <col width="3.1796875" customWidth="1" style="37" min="243" max="243"/>
     <col width="11.36328125" customWidth="1" style="37" min="244" max="244"/>
     <col width="10.1796875" customWidth="1" style="37" min="245" max="245"/>
